--- a/Dataweave AI.xlsx
+++ b/Dataweave AI.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myoffice.accenture.com/personal/varun_c_kumar_singh_accenture_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{E2D2082F-B7BB-4309-9FDE-5E114FD9B995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{681C91EF-B326-499C-9DE9-27806EEC9922}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{E2D2082F-B7BB-4309-9FDE-5E114FD9B995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4715D2EA-3064-4AF4-BFC9-FAFA750E7AB7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{87BBF661-ED2F-4C1F-BDCD-640CD176D2E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,6 +42,12 @@
   </si>
   <si>
     <t>Output</t>
+  </si>
+  <si>
+    <t>DWL geneated from MuleSoft Vibes</t>
+  </si>
+  <si>
+    <t>Prompt</t>
   </si>
   <si>
     <t>{
@@ -113,26 +119,8 @@
 }</t>
   </si>
   <si>
-    <t>DWL geneated from MuleSoft Vibes</t>
-  </si>
-  <si>
-    <t>%dw 2.0
-output application/json
----
-{
-  flights: payload.Flights.*Flight filter (\$.AvailableSeats as Number &gt; 0) map (flight, index) -&gt; {
-    flightId: flight.FlightId,
-    departureCity: flight.DepartureCity,
-    arrivalCity: flight.ArrivalCity,
-    options: flight.Options.*Option map (option, optionIndex) -&gt; {
-      id: option.Id,
-      category: option.Category,
-      price: if (option.Category == "Domestic") (option.Price as Number) * 1.1 else (option.Price as Number)
-    }
-  },
-  allOptionIds: flatten(payload.Flights.*Flight filter (\$.AvailableSeats as Number &gt; 0) map (flight, index) -&gt; flight.Options.*Option map (option, optionIndex) -&gt; option.Id),
-  totalOptions: sizeOf(flatten(payload.Flights.*Flight filter (\$.AvailableSeats as Number &gt; 0) map (flight, index) -&gt; flight.Options.*Option map (option, optionIndex) -&gt; option.Id))
-}</t>
+    <t xml:space="preserve">"Generate a DataWeave 2.0 script to transform a JSON payload to a new JSON structure. Map Field1 to Field2 in uppercase and remove dashes from phone number. Add new field as booking date with current date timestamp.  
+</t>
   </si>
   <si>
     <t>&lt;Flights&gt;
@@ -196,31 +184,48 @@
   </si>
   <si>
     <t>%dw 2.0
-output application/xml
+output application/json
 ---
 {
-  PNRData: {
-    Passenger: {
-      Name: payload.passenger.name,
-      FlightNumber: payload.passenger.flightNumber,
-      TravelDate: payload.passenger.date as Date {format: "MM/dd/yyyy"} as String {format: "yyyy-MM-dd"},
-      SpecialAssistance: if (payload.passenger.class == "Business") true else false
+  flights: payload.Flights.*Flight filter ($.AvailableSeats as Number &gt; 0) map (flight, index) -&gt; {
+    flightId: flight.FlightId,
+    departureCity: flight.DepartureCity,
+    arrivalCity: flight.ArrivalCity,
+    options: flight.Options.*Option map (option, optionIndex) -&gt; {
+      id: option.Id,
+      category: option.Category,
+      price: if (option.Category == "Domestic") (option.Price as Number) * 1.1 else (option.Price as Number)
+    }
+  },
+  allOptionIds: flatten(payload.Flights.*Flight filter ($.AvailableSeats as Number &gt; 0) map (flight, index) -&gt; flight.Options.*Option map (option, optionIndex) -&gt; option.Id),
+  totalOptions: sizeOf(flatten(payload.Flights.*Flight filter ($.AvailableSeats as Number &gt; 0) map (flight, index) -&gt; flight.Options.*Option map (option, optionIndex) -&gt; option.Id))
+}</t>
+  </si>
+  <si>
+    <t>Generate DataWeave 2.0 code to map the following XML payload into JSON output structure. Apply skip null everywhere and Extract FlightId, DepartureCity, and ArrivalCity. Use the map operator to update the price by multiplying it by 1.1 (10% tax) for all items where the category is Domestic. Filter out flights where AvailableSeats is less than 1AvailableSeats. Flatten on the nested flight options array, extract the  IDs, and calculate the total count.</t>
+  </si>
+  <si>
+    <t>{
+  "passenger": {
+    "name": "Alex Johnson",
+    "flightNumber": "AI202",
+    "date": "04/15/2026",
+    "class": "Business"
+  },
+  "baggage": [
+    {
+      "id": "B1",
+      "weight": 25
     },
-    BaggageDetails: {
-      NormalBaggage: {
-        Baggage: (payload.baggage filter (item) -&gt; item.weight &lt;= 30) map {
-          Id: \$.id,
-          Weight: \$.weight
-        }
-      },
-      HeavyBaggage: {
-        Baggage: (payload.baggage filter (item) -&gt; item.weight &gt; 30) map {
-          Id: \$.id,
-          Weight: \$.weight
-        }
-      }
+    {
+      "id": "B2",
+      "weight": 32
+    },
+    {
+      "id": "B3",
+      "weight": 18
     }
-  }
+  ]
 }</t>
   </si>
   <si>
@@ -252,27 +257,32 @@
 &lt;/PNRData&gt;</t>
   </si>
   <si>
-    <t>{
-  "passenger": {
-    "name": "Alex Johnson",
-    "flightNumber": "AI202",
-    "date": "04/15/2026",
-    "class": "Business"
-  },
-  "baggage": [
-    {
-      "id": "B1",
-      "weight": 25
+    <t>%dw 2.0
+output application/xml
+---
+{
+  PNRData: {
+    Passenger: {
+      Name: payload.passenger.name,
+      FlightNumber: payload.passenger.flightNumber,
+      TravelDate: payload.passenger.date as Date {format: "MM/dd/yyyy"} as String {format: "yyyy-MM-dd"},
+      SpecialAssistance: if (payload.passenger.class == "Business") true else false
     },
-    {
-      "id": "B2",
-      "weight": 32
-    },
-    {
-      "id": "B3",
-      "weight": 18
+    BaggageDetails: {
+      NormalBaggage: {
+        Baggage: (payload.baggage filter (item) -&gt; item.weight &lt;= 30) map {
+          Id: $.id,
+          Weight: $.weight
+        }
+      },
+      HeavyBaggage: {
+        Baggage: (payload.baggage filter (item) -&gt; item.weight &gt; 30) map {
+          Id: $.id,
+          Weight: $.weight
+        }
+      }
     }
-  ]
+  }
 }</t>
   </si>
   <si>
@@ -295,52 +305,6 @@
 •	Conditionals: Using if-else or case statements for class validation.
 •	Date Formatting: Using as Date {format: "..."} and as String {format: "..."}.
 •	Output Control: Handling XML attributes and structured nodes.</t>
-  </si>
-  <si>
-    <t>Prompt</t>
-  </si>
-  <si>
-    <t>%dw 2.0
-output application/json skipNullOn="everywhere"
-import dw::core::Dates
-import dw::util::Coercions
----
-{
-  flights: payload.Flights.Flight
-    filter (\$.Status != "CANCELLED")
-    map ( flight , index ) -&gt; {
-      flightId: flight.FlightId,
-      source: if (flight.Source == "JFK") "John F. Kennedy" else flight.Source,
-      destination: flight.Destination,
-      price: flight.Price as Number, // Coerce to Number, will be skipped if empty due to skipNullOn
-      departureTime: flight.DeptTime as LocalDateTime {format: "yyyy-MM-dd'T'HH:mm:ss"}, // Coerce to LocalDateTime, will be skipped if empty
-      status: if (flight.Status == "CONFIRMED") "Open" else flight.Status
-    },
-  processedAt: now() as String {format: "yyyy-MM-dd'T'HH:mm:ss'Z'"}
-}</t>
-  </si>
-  <si>
-    <t>{
-  "flights": [
-    {
-      "flightId": "F201",
-      "source": "John F. Kennedy",
-      "destination": "LAX",
-      "price": 350.50,
-      "departureTime": "2026-04-05T10:30:00",
-      "status": "Open"
-    },
-    {
-      "flightId": "F203",
-      "source": "John F. Kennedy",
-      "destination": "SFO",
-      "price": 500.00,
-      "departureTime": null,
-      "status": "Open"
-    }
-  ],
-  "processedAt": "2026-04-01T10:15:30Z"
-}</t>
   </si>
   <si>
     <t>&lt;FlightsResponse&gt;
@@ -373,6 +337,62 @@
 &lt;/FlightsResponse&gt;</t>
   </si>
   <si>
+    <t>{
+  "flights": [
+    {
+      "flightId": "F201",
+      "source": "John F. Kennedy",
+      "destination": "LAX",
+      "price": 350.50,
+      "departureTime": "2026-04-05T10:30:00",
+      "status": "Open"
+    },
+    {
+      "flightId": "F203",
+      "source": "John F. Kennedy",
+      "destination": "SFO",
+      "price": 500.00,
+      "departureTime": null,
+      "status": "Open"
+    }
+  ],
+  "processedAt": "2026-04-01T10:15:30Z"
+}</t>
+  </si>
+  <si>
+    <t>%dw 2.0
+output application/json
+var airportMap = {
+    "JFK": "John F. Kennedy",
+    "LHR": "London Heathrow"
+}
+var flights = (payload.FlightsResponse.Flights.*Flight default [])
+---
+{
+  flights: (
+      flights
+        filter ((flight) -&gt; (flight.Status as String) == "CONFIRMED")
+        map (flight) -&gt; {
+            flightId: flight.FlightId as String,
+            source: airportMap[flight.Source as String] default (flight.Source as String),
+            destination: flight.Destination as String,
+            price: 
+                if (isEmpty(flight.Price)) 
+                    null 
+                else 
+                    ((flight.Price as Number) as String {format: "##0.00"}) as Number,
+            departureTime: 
+                if (isEmpty(flight.DeptTime)) 
+                    null 
+                else 
+                    (flight.DeptTime as LocalDateTime),
+            status: "Open"
+        }
+  ),
+  processedAt: now() as String {format: "yyyy-MM-dd'T'HH:mm:ss'Z'"}
+}</t>
+  </si>
+  <si>
     <t>Generate a DataWeave 2.0 script for an airline integration scenario.
 Goal: Transform incoming raw flight data from a legacy SOAP system (XML) into a standardized JSON format for a modern booking API.
 Input Structure (XML): &lt;Provide input XML payload&gt;
@@ -384,19 +404,12 @@
 4.	Scenario D - Formatting: The output must be JSON. Add a field processedAt using the current timestamp.
 5.	Handling Errors: Provide robust handling for missing fields, ensuring empty strings are not passed to numerical fields.</t>
   </si>
-  <si>
-    <t xml:space="preserve">"Generate a DataWeave 2.0 script to transform a JSON payload to a new JSON structure. Map Field1 to Field2 in uppercase and remove dashes from phone number. Add new field as booking date with current date timestamp.  
-</t>
-  </si>
-  <si>
-    <t>Generate DataWeave 2.0 code to map the following XML payload into JSON output structure. Apply skip null everywhere and Extract FlightId, DepartureCity, and ArrivalCity. Use the map operator to update the price by multiplying it by 1.1 (10% tax) for all items where the category is Domestic. Filter out flights where AvailableSeats is less than 1AvailableSeats. Flatten on the nested flight options array, extract the  IDs, and calculate the total count.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -781,15 +794,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C347D3AA-D348-4C59-9529-274F90537A24}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="27.54296875" customWidth="1"/>
-    <col min="2" max="2" width="23.08984375" customWidth="1"/>
-    <col min="3" max="3" width="37.81640625" customWidth="1"/>
-    <col min="4" max="4" width="44.08984375" customWidth="1"/>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="37.85546875" customWidth="1"/>
+    <col min="4" max="4" width="44.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -797,71 +810,292 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="375.75">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="409.6">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="362.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="409.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="409.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="409.6">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="201e516f-dd92-4e20-9f67-6935358eea2d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c5147dc6-5dc7-40b1-89df-6a5f63e3bef8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D0FE575DE0C53A4F959313DF00308DE0" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77d845a3ba730a9ad78a5688532b42d3">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c5147dc6-5dc7-40b1-89df-6a5f63e3bef8" xmlns:ns3="201e516f-dd92-4e20-9f67-6935358eea2d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a57932cc3b142d69a0bdd30f90f56525" ns2:_="" ns3:_="">
+    <xsd:import namespace="c5147dc6-5dc7-40b1-89df-6a5f63e3bef8"/>
+    <xsd:import namespace="201e516f-dd92-4e20-9f67-6935358eea2d"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c5147dc6-5dc7-40b1-89df-6a5f63e3bef8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6d165d17-9b79-46c3-82b9-c927e733c429" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="201e516f-dd92-4e20-9f67-6935358eea2d" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c58df37d-8ea3-4377-9b63-b22576f075c0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="201e516f-dd92-4e20-9f67-6935358eea2d">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD6A456B-046E-436D-AE96-D26AA20940C1}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC59EB8F-6DEB-4EFF-8B70-9E0975D99CAC}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D69CC10-8DD8-42CB-AB97-333B1B7D5649}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
